--- a/GRAMMAR/1_21_07.xlsx
+++ b/GRAMMAR/1_21_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CB10749E-45F2-4E73-AD9B-8A6FD333EA14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E54AB528-0C3A-4356-8CC0-0539ED3F006A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10560" yWindow="915" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="1560" windowWidth="27840" windowHeight="20040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -278,9 +278,6 @@
   </si>
   <si>
     <t>をとわず</t>
-  </si>
-  <si>
-    <t>にあたって</t>
   </si>
   <si>
     <t>在……之际(重要时刻)</t>
@@ -498,12 +495,36 @@
     <t>(1)发现(2)如果</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">动词原形 + </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="宋体"/>
+        <family val="3"/>
+        <charset val="134"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>にあたって</t>
+    </r>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -541,6 +562,13 @@
       <family val="2"/>
       <charset val="128"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -1081,13 +1109,13 @@
         <v>2</v>
       </c>
       <c r="B15" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="D15" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.15">
@@ -1373,10 +1401,10 @@
         <v>0</v>
       </c>
       <c r="B38" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="C38" s="2" t="s">
         <v>86</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>87</v>
       </c>
       <c r="D38" s="2"/>
     </row>
@@ -1385,13 +1413,13 @@
         <v>0</v>
       </c>
       <c r="B39" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="C39" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="D39" s="2" t="s">
         <v>89</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.15">
@@ -1399,13 +1427,13 @@
         <v>0</v>
       </c>
       <c r="B40" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="C40" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C40" s="2" t="s">
+      <c r="D40" s="2" t="s">
         <v>92</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
@@ -1413,10 +1441,10 @@
         <v>0</v>
       </c>
       <c r="B41" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="C41" s="2" t="s">
         <v>94</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>95</v>
       </c>
       <c r="D41" s="2"/>
     </row>
@@ -1425,10 +1453,10 @@
         <v>0</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="C42" s="2" t="s">
         <v>96</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>97</v>
       </c>
       <c r="D42" s="2"/>
     </row>
@@ -1437,10 +1465,10 @@
         <v>0</v>
       </c>
       <c r="B43" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C43" s="2" t="s">
         <v>98</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>99</v>
       </c>
       <c r="D43" s="2"/>
     </row>
@@ -1449,13 +1477,13 @@
         <v>0</v>
       </c>
       <c r="B44" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C44" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C44" s="2" t="s">
+      <c r="D44" s="2" t="s">
         <v>101</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
@@ -1463,10 +1491,10 @@
         <v>0</v>
       </c>
       <c r="B45" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="C45" s="2" t="s">
         <v>103</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="D45" s="2"/>
     </row>
@@ -1475,10 +1503,10 @@
         <v>0</v>
       </c>
       <c r="B46" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="C46" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>106</v>
       </c>
       <c r="D46" s="2"/>
     </row>
@@ -1487,10 +1515,10 @@
         <v>0</v>
       </c>
       <c r="B47" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C47" s="2" t="s">
         <v>107</v>
-      </c>
-      <c r="C47" s="2" t="s">
-        <v>108</v>
       </c>
       <c r="D47" s="2"/>
     </row>
@@ -1499,10 +1527,10 @@
         <v>0</v>
       </c>
       <c r="B48" s="2" t="s">
+        <v>108</v>
+      </c>
+      <c r="C48" s="2" t="s">
         <v>109</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>110</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>14</v>
@@ -1513,10 +1541,10 @@
         <v>0</v>
       </c>
       <c r="B49" s="2" t="s">
+        <v>110</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>111</v>
-      </c>
-      <c r="C49" s="2" t="s">
-        <v>112</v>
       </c>
       <c r="D49" s="2"/>
     </row>
@@ -1525,10 +1553,10 @@
         <v>0</v>
       </c>
       <c r="B50" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="C50" s="2" t="s">
         <v>113</v>
-      </c>
-      <c r="C50" s="2" t="s">
-        <v>114</v>
       </c>
       <c r="D50" s="2"/>
     </row>
@@ -1537,10 +1565,10 @@
         <v>0</v>
       </c>
       <c r="B51" s="2" t="s">
+        <v>114</v>
+      </c>
+      <c r="C51" s="2" t="s">
         <v>115</v>
-      </c>
-      <c r="C51" s="2" t="s">
-        <v>116</v>
       </c>
       <c r="D51" s="2"/>
     </row>
@@ -1549,10 +1577,10 @@
         <v>0</v>
       </c>
       <c r="B52" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="C52" s="2" t="s">
         <v>117</v>
-      </c>
-      <c r="C52" s="2" t="s">
-        <v>118</v>
       </c>
       <c r="D52" s="2"/>
     </row>
@@ -1564,10 +1592,10 @@
         <v>41</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.15">
@@ -1575,10 +1603,10 @@
         <v>2</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>124</v>
       </c>
       <c r="D54" s="2"/>
     </row>
@@ -1587,10 +1615,10 @@
         <v>2</v>
       </c>
       <c r="B55" s="2" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D55" s="2"/>
     </row>
@@ -1599,10 +1627,10 @@
         <v>2</v>
       </c>
       <c r="B56" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D56" s="2"/>
     </row>
@@ -1611,10 +1639,10 @@
         <v>2</v>
       </c>
       <c r="B57" s="2" t="s">
+        <v>126</v>
+      </c>
+      <c r="C57" s="2" t="s">
         <v>127</v>
-      </c>
-      <c r="C57" s="2" t="s">
-        <v>128</v>
       </c>
       <c r="D57" s="2"/>
     </row>

--- a/GRAMMAR/1_21_07.xlsx
+++ b/GRAMMAR/1_21_07.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF44AFDF-7C74-47D3-A5AD-A3E8273DC13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6030F89A-760F-4D22-BA22-1CF331CBCA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="10275" yWindow="690" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="120">
   <si>
     <t>Fre</t>
   </si>
@@ -34,6 +34,48 @@
     <t>备注</t>
   </si>
   <si>
+    <t>だし</t>
+  </si>
+  <si>
+    <t>因果，理由</t>
+  </si>
+  <si>
+    <t>取り入れる</t>
+  </si>
+  <si>
+    <t>引进;采纳</t>
+  </si>
+  <si>
+    <t>やりだす</t>
+  </si>
+  <si>
+    <t>开始做；着手进行</t>
+  </si>
+  <si>
+    <t>どうも〜らしい（ようだ、みたいだ）</t>
+  </si>
+  <si>
+    <t>推测</t>
+  </si>
+  <si>
+    <t>伺う</t>
+  </si>
+  <si>
+    <t>「聞く·尋ねる·問う」的自谦</t>
+  </si>
+  <si>
+    <t>うかがう</t>
+  </si>
+  <si>
+    <t>〜どころか</t>
+  </si>
+  <si>
+    <t>别说…就连…</t>
+  </si>
+  <si>
+    <t>hello</t>
+  </si>
+  <si>
     <t>ちっとも</t>
   </si>
   <si>
@@ -43,19 +85,16 @@
     <t>后接否定</t>
   </si>
   <si>
-    <t>だし</t>
-  </si>
-  <si>
-    <t>因果，理由</t>
-  </si>
-  <si>
-    <t>やりだす</t>
-  </si>
-  <si>
-    <t>开始做；着手进行</t>
-  </si>
-  <si>
-    <t>引进;采纳</t>
+    <t>どうも</t>
+  </si>
+  <si>
+    <t>(1)似乎；总觉得 (2)十分；非常；实在</t>
+  </si>
+  <si>
+    <t>だるい</t>
+  </si>
+  <si>
+    <t>疲倦的；无力的</t>
   </si>
   <si>
     <t>ちゃって</t>
@@ -64,12 +103,6 @@
     <t>てしまう口语</t>
   </si>
   <si>
-    <t>どうも〜らしい（ようだ、みたいだ）</t>
-  </si>
-  <si>
-    <t>推测</t>
-  </si>
-  <si>
     <t>にかぎって</t>
   </si>
   <si>
@@ -79,7 +112,10 @@
     <t>に限って</t>
   </si>
   <si>
-    <t>怎么办</t>
+    <t>おかしい</t>
+  </si>
+  <si>
+    <t>奇怪的；滑稽的</t>
   </si>
   <si>
     <t>ていない</t>
@@ -91,106 +127,241 @@
     <t>后面不能直接{と}，而是{しないと}</t>
   </si>
   <si>
-    <t>尊他语</t>
-  </si>
-  <si>
-    <t>疲倦的；无力的</t>
+    <t>ずっと</t>
+  </si>
+  <si>
+    <t>…得多;很…</t>
+  </si>
+  <si>
+    <t>にもかかわらず</t>
   </si>
   <si>
     <t>虽然</t>
   </si>
   <si>
-    <t>いらっしゃる</t>
-  </si>
-  <si>
-    <t>「行く・来る・いる・ある」の敬語</t>
-  </si>
-  <si>
-    <t>伺う</t>
-  </si>
-  <si>
-    <t>「聞く·尋ねる·問う」的自谦</t>
-  </si>
-  <si>
-    <t>うかがう</t>
-  </si>
-  <si>
-    <t>〜どころか</t>
-  </si>
-  <si>
-    <t>别说…就连…</t>
-  </si>
-  <si>
-    <t>hello</t>
-  </si>
-  <si>
-    <t>～たら</t>
-  </si>
-  <si>
-    <t>(1)发现(2)如果</t>
-  </si>
-  <si>
-    <t>おかしい</t>
-  </si>
-  <si>
-    <t>奇怪的；滑稽的</t>
-  </si>
-  <si>
-    <t>からには</t>
-  </si>
-  <si>
-    <t>既然…就…</t>
-  </si>
-  <si>
-    <t>不是“因为...”</t>
-  </si>
-  <si>
-    <t>どうも</t>
-  </si>
-  <si>
-    <t>(1)似乎；总觉得 (2)十分；非常；实在</t>
+    <t>〜ような</t>
+  </si>
+  <si>
+    <t>有种…样的感觉</t>
+  </si>
+  <si>
+    <t>申す</t>
+  </si>
+  <si>
+    <t>自谦敬语，自我介绍，道歉，请求</t>
+  </si>
+  <si>
+    <t>もうす</t>
+  </si>
+  <si>
+    <t>に際して</t>
+  </si>
+  <si>
+    <t>当...之际(契机)</t>
+  </si>
+  <si>
+    <t>A は B ほど C ない</t>
+  </si>
+  <si>
+    <t>A没有B那么……</t>
+  </si>
+  <si>
+    <t>ほど</t>
+  </si>
+  <si>
+    <t>程度</t>
+  </si>
+  <si>
+    <t>まさか</t>
+  </si>
+  <si>
+    <t>(1)难道… (2)该不会…吧 (3)怎么可能</t>
+  </si>
+  <si>
+    <t>において</t>
+  </si>
+  <si>
+    <t>在…方面；在…时候；在…地点</t>
+  </si>
+  <si>
+    <t>めった</t>
+  </si>
+  <si>
+    <t>几乎不…</t>
+  </si>
+  <si>
+    <t>にかかわらず</t>
+  </si>
+  <si>
+    <t>不论如何；不管怎样</t>
+  </si>
+  <si>
+    <t>せいだ</t>
+  </si>
+  <si>
+    <t>都怪…(句尾)，总结原因</t>
+  </si>
+  <si>
+    <t>を問わず</t>
+  </si>
+  <si>
+    <t>不论，不管</t>
+  </si>
+  <si>
+    <t>をとわず</t>
+  </si>
+  <si>
+    <t>せいで</t>
+  </si>
+  <si>
+    <t>都怪…(句中)</t>
+  </si>
+  <si>
+    <t>さえ</t>
+  </si>
+  <si>
+    <t>极端的例子，从而类推其它事物</t>
+  </si>
+  <si>
+    <t>中性词</t>
+  </si>
+  <si>
+    <t>のに</t>
+  </si>
+  <si>
+    <t>尽管;竟然;明明</t>
+  </si>
+  <si>
+    <t>売り上げ</t>
+  </si>
+  <si>
+    <t>销售额；营业额</t>
+  </si>
+  <si>
+    <t>～うちに</t>
+  </si>
+  <si>
+    <t>在...期间，趁着…</t>
+  </si>
+  <si>
+    <t>N+すら</t>
+  </si>
+  <si>
+    <t>甚至～；连～</t>
+  </si>
+  <si>
+    <t>用于消极</t>
+  </si>
+  <si>
+    <t>どなた</t>
+  </si>
+  <si>
+    <t>哪位人</t>
+  </si>
+  <si>
+    <t>調子</t>
+  </si>
+  <si>
+    <t>状况，样子</t>
+  </si>
+  <si>
+    <t>ちょうし</t>
+  </si>
+  <si>
+    <t>にあたって</t>
+  </si>
+  <si>
+    <t>在……之际(重要时刻)</t>
+  </si>
+  <si>
+    <t>無駄に</t>
+  </si>
+  <si>
+    <t>浪费</t>
+  </si>
+  <si>
+    <t>むだに</t>
+  </si>
+  <si>
+    <t>少なくとも</t>
+  </si>
+  <si>
+    <t>至少；起码</t>
+  </si>
+  <si>
+    <t>申し上げる</t>
+  </si>
+  <si>
+    <t>「言う」的自谦语</t>
+  </si>
+  <si>
+    <t>を通して</t>
+  </si>
+  <si>
+    <t>(1)通过…(人，媒介，经验)(2)在…期间</t>
+  </si>
+  <si>
+    <t>〜ことに</t>
+  </si>
+  <si>
+    <t>令人感到…的是…</t>
   </si>
   <si>
     <t>くせに</t>
   </si>
   <si>
-    <t>「のに」主语既可以是“人”，也可以是“物”</t>
-  </si>
-  <si>
-    <t>どなた</t>
-  </si>
-  <si>
-    <t>哪位人</t>
-  </si>
-  <si>
-    <t>に際して</t>
-  </si>
-  <si>
-    <t>当...之际(契机)</t>
-  </si>
-  <si>
-    <t>申す</t>
-  </si>
-  <si>
-    <t>自谦敬语，自我介绍，道歉，请求</t>
-  </si>
-  <si>
-    <t>もうす</t>
-  </si>
-  <si>
-    <t>ずっと</t>
-  </si>
-  <si>
-    <t>(1)一直...(2)…得多;(3)很…</t>
+    <t>明明；却</t>
+  </si>
+  <si>
+    <t>主语一致</t>
+  </si>
+  <si>
+    <t>左右される</t>
+  </si>
+  <si>
+    <t>被影响</t>
+  </si>
+  <si>
+    <t>なら</t>
+  </si>
+  <si>
+    <t>既然你提到…的话</t>
+  </si>
+  <si>
+    <t>对方说的话被当成一个讨论的主题</t>
+  </si>
+  <si>
+    <t>にかけて</t>
+  </si>
+  <si>
+    <t>在…领域</t>
+  </si>
+  <si>
+    <t>～から～にかけて</t>
+  </si>
+  <si>
+    <t>取り組み</t>
+  </si>
+  <si>
+    <t>举措；对策</t>
+  </si>
+  <si>
+    <t>言われた</t>
+  </si>
+  <si>
+    <t>有人曾说;被说</t>
+  </si>
+  <si>
+    <t>うえに</t>
   </si>
   <si>
     <t>不仅…而且…</t>
   </si>
   <si>
-    <t>〜ことに</t>
-  </si>
-  <si>
-    <t>令人感到…的是…</t>
+    <t>〜の一つ</t>
+  </si>
+  <si>
+    <t>〜之一</t>
   </si>
   <si>
     <t>だったら</t>
@@ -208,244 +379,14 @@
     <t>精确的</t>
   </si>
   <si>
-    <t>を問わず</t>
-  </si>
-  <si>
-    <t>不论，不管</t>
-  </si>
-  <si>
-    <t>をとわず</t>
-  </si>
-  <si>
-    <t>少なくとも</t>
-  </si>
-  <si>
-    <t>至少；起码</t>
-  </si>
-  <si>
-    <t>を通して</t>
-  </si>
-  <si>
-    <t>(1)通过…(人，媒介，经验)(2)在…期间</t>
-  </si>
-  <si>
-    <t>取り組み</t>
-  </si>
-  <si>
-    <t>举措；对策</t>
-  </si>
-  <si>
-    <t>左右される</t>
-  </si>
-  <si>
-    <t>被影响</t>
-  </si>
-  <si>
-    <t>申し上げる</t>
-  </si>
-  <si>
-    <t>「言う」的自谦语</t>
-  </si>
-  <si>
-    <t>なら</t>
-  </si>
-  <si>
-    <t>既然你提到…的话</t>
-  </si>
-  <si>
-    <t>对方说的话被当成一个讨论的主题</t>
-  </si>
-  <si>
-    <t>〜の一つ</t>
-  </si>
-  <si>
-    <t>〜之一</t>
-  </si>
-  <si>
-    <t>言われた</t>
-  </si>
-  <si>
-    <t>有人曾说;被说</t>
-  </si>
-  <si>
-    <t>調子</t>
-  </si>
-  <si>
-    <t>状况，样子</t>
-  </si>
-  <si>
-    <t>ちょうし</t>
-  </si>
-  <si>
-    <t>さえ</t>
-  </si>
-  <si>
-    <t>极端的例子，从而类推其它事物</t>
-  </si>
-  <si>
-    <t>中性词</t>
-  </si>
-  <si>
-    <t>动词原形 + にあたって</t>
-  </si>
-  <si>
-    <t>在……之际(重要时刻)</t>
-  </si>
-  <si>
-    <t>N+すら</t>
-  </si>
-  <si>
-    <t>甚至～；连～</t>
-  </si>
-  <si>
-    <t>用于消极</t>
-  </si>
-  <si>
-    <t>にかかわらず</t>
-  </si>
-  <si>
-    <t>不论如何；不管怎样</t>
-  </si>
-  <si>
-    <t>のに</t>
-  </si>
-  <si>
-    <t>尽管;竟然;明明</t>
-  </si>
-  <si>
-    <t>にかけて</t>
-  </si>
-  <si>
-    <t>在…领域</t>
-  </si>
-  <si>
-    <t>～から～にかけて</t>
-  </si>
-  <si>
-    <t>せいだ</t>
-  </si>
-  <si>
-    <t>都怪…(句尾)，总结原因</t>
-  </si>
-  <si>
-    <t>まさか</t>
-  </si>
-  <si>
-    <t>(1)难道… (2)该不会…吧 (3)怎么可能</t>
-  </si>
-  <si>
-    <t>めった</t>
-  </si>
-  <si>
-    <t>几乎不…</t>
-  </si>
-  <si>
-    <t>せいで</t>
-  </si>
-  <si>
-    <t>都怪…(句中)</t>
-  </si>
-  <si>
-    <t>～うちに</t>
-  </si>
-  <si>
-    <t>在...期间，趁着…</t>
-  </si>
-  <si>
-    <t>ほど</t>
-  </si>
-  <si>
-    <t>程度</t>
-  </si>
-  <si>
-    <t>A は B ほど C ない</t>
-  </si>
-  <si>
-    <t>A没有B那么……</t>
-  </si>
-  <si>
-    <t>売り上げ</t>
-  </si>
-  <si>
-    <t>销售额；营业额</t>
-  </si>
-  <si>
-    <t>において</t>
-  </si>
-  <si>
-    <t>在…方面；在…时候；在…地点</t>
-  </si>
-  <si>
-    <t>無駄に</t>
-  </si>
-  <si>
-    <t>浪费</t>
-  </si>
-  <si>
-    <t>むだに</t>
-  </si>
-  <si>
-    <t>うえに</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>〜</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="宋体"/>
-        <family val="3"/>
-        <charset val="134"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>ような</t>
-    </r>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>像…一样的</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>取り入れる</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>どうしよう</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>お～になる</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>だるい</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>にもかかわらず</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
-    <t>明明~却~(主语是人，前后主语一致)</t>
-    <phoneticPr fontId="3" type="noConversion"/>
+    <t>明明~却~</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -460,30 +401,7 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="宋体"/>
-      <family val="2"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <family val="3"/>
       <charset val="134"/>
@@ -525,12 +443,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -833,7 +750,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D52"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.75" customWidth="1"/>
@@ -859,7 +776,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
         <v>4</v>
@@ -867,38 +784,35 @@
       <c r="C2" t="s">
         <v>5</v>
       </c>
-      <c r="D2" t="s">
-        <v>6</v>
-      </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A4">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C4" t="s">
         <v>9</v>
-      </c>
-      <c r="C4" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A5">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
-        <v>124</v>
+        <v>10</v>
       </c>
       <c r="C5" t="s">
         <v>11</v>
@@ -906,7 +820,7 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A6">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="B6" t="s">
         <v>12</v>
@@ -914,66 +828,69 @@
       <c r="C6" t="s">
         <v>13</v>
       </c>
+      <c r="D6" t="s">
+        <v>14</v>
+      </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>16</v>
+      </c>
+      <c r="D7" t="s">
+        <v>17</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A8">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D8" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="16.5" x14ac:dyDescent="0.3">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A9">
         <v>2</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>122</v>
+      <c r="B9" t="s">
+        <v>21</v>
       </c>
       <c r="C9" t="s">
-        <v>123</v>
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A10">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B10" t="s">
-        <v>125</v>
+        <v>23</v>
       </c>
       <c r="C10" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A11">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="C11" t="s">
-        <v>21</v>
-      </c>
-      <c r="D11" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.15">
@@ -981,21 +898,24 @@
         <v>3</v>
       </c>
       <c r="B12" t="s">
-        <v>126</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>23</v>
+        <v>28</v>
+      </c>
+      <c r="D12" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A13">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B13" t="s">
-        <v>127</v>
+        <v>30</v>
       </c>
       <c r="C13" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.15">
@@ -1003,168 +923,165 @@
         <v>3</v>
       </c>
       <c r="B14" t="s">
-        <v>128</v>
+        <v>32</v>
       </c>
       <c r="C14" t="s">
-        <v>25</v>
+        <v>33</v>
+      </c>
+      <c r="D14" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A16">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B16" t="s">
-        <v>28</v>
+        <v>37</v>
       </c>
       <c r="C16" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A17">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="B17" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C17" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" t="s">
-        <v>33</v>
+        <v>40</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A18">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B18" t="s">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="C18" t="s">
-        <v>35</v>
+        <v>42</v>
+      </c>
+      <c r="D18" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A19">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="B19" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C19" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A20">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B20" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
-      </c>
-      <c r="D20" t="s">
-        <v>40</v>
+        <v>47</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A21">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B21" t="s">
-        <v>41</v>
+        <v>48</v>
       </c>
       <c r="C21" t="s">
-        <v>42</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A22">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="B22" t="s">
-        <v>43</v>
+        <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>129</v>
-      </c>
-      <c r="D22" t="s">
-        <v>44</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A23">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B23" t="s">
-        <v>45</v>
+        <v>52</v>
       </c>
       <c r="C23" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A24">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B24" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="C24" t="s">
-        <v>48</v>
+        <v>55</v>
+      </c>
+      <c r="D24" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A25">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B25" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="C25" t="s">
-        <v>50</v>
-      </c>
-      <c r="D25" t="s">
-        <v>51</v>
+        <v>57</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A26">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B26" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A27">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>60</v>
       </c>
       <c r="C27" t="s">
-        <v>54</v>
+        <v>61</v>
+      </c>
+      <c r="D27" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.15">
@@ -1172,10 +1089,10 @@
         <v>0</v>
       </c>
       <c r="B28" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.15">
@@ -1183,13 +1100,13 @@
         <v>0</v>
       </c>
       <c r="B29" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C29" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="D29" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.15">
@@ -1197,10 +1114,10 @@
         <v>0</v>
       </c>
       <c r="B30" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C30" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.15">
@@ -1208,13 +1125,10 @@
         <v>0</v>
       </c>
       <c r="B31" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C31" t="s">
-        <v>63</v>
-      </c>
-      <c r="D31" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.15">
@@ -1222,10 +1136,10 @@
         <v>0</v>
       </c>
       <c r="B32" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C32" t="s">
-        <v>66</v>
+        <v>73</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.15">
@@ -1233,21 +1147,24 @@
         <v>0</v>
       </c>
       <c r="B33" t="s">
-        <v>67</v>
+        <v>74</v>
       </c>
       <c r="C33" t="s">
-        <v>68</v>
+        <v>75</v>
+      </c>
+      <c r="D33" t="s">
+        <v>76</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A34">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B34" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.15">
@@ -1255,10 +1172,13 @@
         <v>0</v>
       </c>
       <c r="B35" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C35" t="s">
-        <v>72</v>
+        <v>80</v>
+      </c>
+      <c r="D35" t="s">
+        <v>81</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.15">
@@ -1266,10 +1186,10 @@
         <v>0</v>
       </c>
       <c r="B36" t="s">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="C36" t="s">
-        <v>74</v>
+        <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.15">
@@ -1277,13 +1197,13 @@
         <v>0</v>
       </c>
       <c r="B37" t="s">
-        <v>75</v>
+        <v>84</v>
       </c>
       <c r="C37" t="s">
-        <v>76</v>
+        <v>85</v>
       </c>
       <c r="D37" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.15">
@@ -1291,10 +1211,10 @@
         <v>0</v>
       </c>
       <c r="B38" t="s">
-        <v>78</v>
+        <v>87</v>
       </c>
       <c r="C38" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.15">
@@ -1302,10 +1222,10 @@
         <v>0</v>
       </c>
       <c r="B39" t="s">
-        <v>80</v>
+        <v>89</v>
       </c>
       <c r="C39" t="s">
-        <v>81</v>
+        <v>90</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.15">
@@ -1313,13 +1233,10 @@
         <v>0</v>
       </c>
       <c r="B40" t="s">
-        <v>82</v>
+        <v>91</v>
       </c>
       <c r="C40" t="s">
-        <v>83</v>
-      </c>
-      <c r="D40" t="s">
-        <v>84</v>
+        <v>92</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.15">
@@ -1327,24 +1244,24 @@
         <v>0</v>
       </c>
       <c r="B41" t="s">
-        <v>85</v>
+        <v>93</v>
       </c>
       <c r="C41" t="s">
-        <v>86</v>
-      </c>
-      <c r="D41" t="s">
-        <v>87</v>
+        <v>94</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.15">
       <c r="A42">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="B42" t="s">
-        <v>88</v>
+        <v>95</v>
       </c>
       <c r="C42" t="s">
-        <v>89</v>
+        <v>96</v>
+      </c>
+      <c r="D42" t="s">
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.15">
@@ -1352,13 +1269,10 @@
         <v>0</v>
       </c>
       <c r="B43" t="s">
-        <v>90</v>
+        <v>98</v>
       </c>
       <c r="C43" t="s">
-        <v>91</v>
-      </c>
-      <c r="D43" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.15">
@@ -1366,10 +1280,13 @@
         <v>0</v>
       </c>
       <c r="B44" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="C44" t="s">
-        <v>94</v>
+        <v>101</v>
+      </c>
+      <c r="D44" t="s">
+        <v>102</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.15">
@@ -1377,10 +1294,13 @@
         <v>0</v>
       </c>
       <c r="B45" t="s">
-        <v>95</v>
+        <v>103</v>
       </c>
       <c r="C45" t="s">
-        <v>96</v>
+        <v>104</v>
+      </c>
+      <c r="D45" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.15">
@@ -1388,13 +1308,10 @@
         <v>0</v>
       </c>
       <c r="B46" t="s">
-        <v>97</v>
+        <v>106</v>
       </c>
       <c r="C46" t="s">
-        <v>98</v>
-      </c>
-      <c r="D46" t="s">
-        <v>99</v>
+        <v>107</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.15">
@@ -1402,10 +1319,10 @@
         <v>0</v>
       </c>
       <c r="B47" t="s">
-        <v>100</v>
+        <v>108</v>
       </c>
       <c r="C47" t="s">
-        <v>101</v>
+        <v>109</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.15">
@@ -1413,10 +1330,10 @@
         <v>0</v>
       </c>
       <c r="B48" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="C48" t="s">
-        <v>103</v>
+        <v>111</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.15">
@@ -1424,13 +1341,10 @@
         <v>0</v>
       </c>
       <c r="B49" t="s">
-        <v>104</v>
+        <v>112</v>
       </c>
       <c r="C49" t="s">
-        <v>105</v>
-      </c>
-      <c r="D49" t="s">
-        <v>6</v>
+        <v>113</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.15">
@@ -1438,10 +1352,13 @@
         <v>0</v>
       </c>
       <c r="B50" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="C50" t="s">
-        <v>107</v>
+        <v>115</v>
+      </c>
+      <c r="D50" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.15">
@@ -1449,10 +1366,10 @@
         <v>0</v>
       </c>
       <c r="B51" t="s">
-        <v>108</v>
+        <v>117</v>
       </c>
       <c r="C51" t="s">
-        <v>109</v>
+        <v>118</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.15">
@@ -1460,61 +1377,14 @@
         <v>0</v>
       </c>
       <c r="B52" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C52" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="53" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A53">
-        <v>0</v>
-      </c>
-      <c r="B53" t="s">
-        <v>112</v>
-      </c>
-      <c r="C53" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="54" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A54">
-        <v>0</v>
-      </c>
-      <c r="B54" t="s">
-        <v>114</v>
-      </c>
-      <c r="C54" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="55" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A55">
-        <v>0</v>
-      </c>
-      <c r="B55" t="s">
-        <v>116</v>
-      </c>
-      <c r="C55" t="s">
-        <v>117</v>
-      </c>
-    </row>
-    <row r="56" spans="1:4" x14ac:dyDescent="0.15">
-      <c r="A56">
-        <v>0</v>
-      </c>
-      <c r="B56" t="s">
-        <v>118</v>
-      </c>
-      <c r="C56" t="s">
         <v>119</v>
       </c>
-      <c r="D56" t="s">
-        <v>120</v>
-      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="3" type="noConversion"/>
+  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>

--- a/GRAMMAR/1_21_07.xlsx
+++ b/GRAMMAR/1_21_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF44AFDF-7C74-47D3-A5AD-A3E8273DC13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A589134-10F7-44CA-84E4-A5333BC8A8D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10275" yWindow="690" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="22005" yWindow="1410" windowWidth="20880" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="131" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="165" uniqueCount="164">
   <si>
     <t>Fre</t>
   </si>
@@ -438,6 +438,142 @@
   </si>
   <si>
     <t>明明~却~(主语是人，前后主语一致)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>意向形ようとする</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>正准备要～（发生了意外的事情）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>に先立って</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>在～之前</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>名+ぶりに</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>时隔～之后再～</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>～か～ないかのうちに</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>刚一…就……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>动た/名の+あげくに</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>结果，终究…（消极）</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>连体形+くせに</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虽然～可是～</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ながらも</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>虽然……但是</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>ものを</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>明明……却</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>～てもはじまらない</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>即使…也没用</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>名+まで</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>甚至连～</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>简体+くらいだ</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>简直到了…的程度</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>名/动原/动た+きり</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>只…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>动原+べきだった</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>之前应该……的(对过去的事情的后悔和反省)</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>动ます形+がたい</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>难以…很难…</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>动原+までになる</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>经过很长一段时间（努力），最终变成……的结果。</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>名+にともなって</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>随着……</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>普通型（名だ）+だけに</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>不愧是……，正因为……</t>
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
@@ -525,12 +661,15 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -833,7 +972,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D73"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.75" customWidth="1"/>
@@ -1513,6 +1652,193 @@
         <v>120</v>
       </c>
     </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A57">
+        <v>3</v>
+      </c>
+      <c r="B57" t="s">
+        <v>130</v>
+      </c>
+      <c r="C57" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A58">
+        <v>3</v>
+      </c>
+      <c r="B58" t="s">
+        <v>132</v>
+      </c>
+      <c r="C58" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A59">
+        <v>3</v>
+      </c>
+      <c r="B59" t="s">
+        <v>134</v>
+      </c>
+      <c r="C59" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A60">
+        <v>3</v>
+      </c>
+      <c r="B60" t="s">
+        <v>136</v>
+      </c>
+      <c r="C60" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A61">
+        <v>3</v>
+      </c>
+      <c r="B61" t="s">
+        <v>138</v>
+      </c>
+      <c r="C61" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A62">
+        <v>3</v>
+      </c>
+      <c r="B62" t="s">
+        <v>140</v>
+      </c>
+      <c r="C62" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A63">
+        <v>3</v>
+      </c>
+      <c r="B63" t="s">
+        <v>142</v>
+      </c>
+      <c r="C63" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.15">
+      <c r="A64">
+        <v>3</v>
+      </c>
+      <c r="B64" t="s">
+        <v>144</v>
+      </c>
+      <c r="C64" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="65" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A65">
+        <v>3</v>
+      </c>
+      <c r="B65" t="s">
+        <v>146</v>
+      </c>
+      <c r="C65" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="66" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A66">
+        <v>3</v>
+      </c>
+      <c r="B66" t="s">
+        <v>148</v>
+      </c>
+      <c r="C66" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="67" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A67">
+        <v>3</v>
+      </c>
+      <c r="B67" t="s">
+        <v>150</v>
+      </c>
+      <c r="C67" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="68" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A68">
+        <v>3</v>
+      </c>
+      <c r="B68" t="s">
+        <v>152</v>
+      </c>
+      <c r="C68" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="69" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A69">
+        <v>3</v>
+      </c>
+      <c r="B69" t="s">
+        <v>154</v>
+      </c>
+      <c r="C69" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A70">
+        <v>3</v>
+      </c>
+      <c r="B70" t="s">
+        <v>156</v>
+      </c>
+      <c r="C70" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A71">
+        <v>3</v>
+      </c>
+      <c r="B71" t="s">
+        <v>158</v>
+      </c>
+      <c r="C71" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A72">
+        <v>3</v>
+      </c>
+      <c r="B72" t="s">
+        <v>160</v>
+      </c>
+      <c r="C72" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="73" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A73">
+        <v>3</v>
+      </c>
+      <c r="B73" t="s">
+        <v>162</v>
+      </c>
+      <c r="C73" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/GRAMMAR/1_21_07.xlsx
+++ b/GRAMMAR/1_21_07.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\N2_2025_12\GRAMMAR\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF5886A4-CBCF-4C6F-AEBF-63CE6B7653FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90D9B957-0665-418A-B471-23D2872AF94D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15405" yWindow="1005" windowWidth="22995" windowHeight="19995" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="201">
   <si>
     <t>Fre</t>
   </si>
@@ -741,6 +741,14 @@
   </si>
   <si>
     <t>不仅仅是；不只是</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>そこで</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>因果关系，于是…</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -1166,7 +1174,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E88"/>
+  <dimension ref="A1:E89"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="8.75" customWidth="1"/>
@@ -2216,6 +2224,17 @@
         <v>198</v>
       </c>
     </row>
+    <row r="89" spans="1:4" ht="18.75" x14ac:dyDescent="0.4">
+      <c r="A89">
+        <v>2</v>
+      </c>
+      <c r="B89" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>200</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
